--- a/tasklist/Book1.xlsx
+++ b/tasklist/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cre\Downloads\tasklist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cre\Downloads\puzzle\tasklist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDC28314-C73A-42A2-8C7E-D12F7D5FEB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D73A0E-A15D-4B28-B565-CA07526B732C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5640FF13-D763-4D1F-AF4F-57189BCD2DF3}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
   <si>
     <t>パズルボブルのタスクリスト</t>
     <phoneticPr fontId="1"/>
@@ -317,6 +317,328 @@
     <t>無理かも</t>
     <rPh sb="0" eb="2">
       <t>ムリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ球の色を消す</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ケ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>同じ球の色が3つ揃ったら消す機構を作る</t>
+    <rPh sb="0" eb="1">
+      <t>オナ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ケ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>キコウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マッチング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いけるよね</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>物理演算の追加</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンザン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>根元を壊されたら下の球が落ちるようにする機構を追加</t>
+    <rPh sb="0" eb="2">
+      <t>ネモト</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>シタ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>キコウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>物理演算</t>
+    <rPh sb="0" eb="2">
+      <t>ブツリ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンザン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上の壁が迫ってくる</t>
+    <rPh sb="0" eb="1">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>セマ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一定時間ごとに上から壁が迫ってくる機構を追加</t>
+    <rPh sb="0" eb="4">
+      <t>イッテイジカン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>セマ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>キコウ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>上に壁をつける</t>
+    <rPh sb="0" eb="1">
+      <t>ウエ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カベ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>壁押し寄せ</t>
+    <rPh sb="0" eb="1">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="1" eb="2">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヨ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバーを作る</t>
+    <rPh sb="8" eb="9">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバー条件とゲームオーバー画面を作る</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバー画面と背景</t>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ハイケイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ゲームオーバー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どんどん壁が押し寄せてきて発射機構のところにある線を玉が越えたらゲームオーバー画面に移行する(ただし根元を壊され落下した玉は線を越えてもゲームオーバー画面に移行しないように変更しなければならない)</t>
+    <rPh sb="4" eb="5">
+      <t>カベ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="13" eb="17">
+      <t>ハッシャキコウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="28" eb="29">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="42" eb="44">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>ネモト</t>
+    </rPh>
+    <rPh sb="53" eb="54">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="56" eb="58">
+      <t>ラッカ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>タマ</t>
+    </rPh>
+    <rPh sb="62" eb="63">
+      <t>セン</t>
+    </rPh>
+    <rPh sb="64" eb="65">
+      <t>コ</t>
+    </rPh>
+    <rPh sb="75" eb="77">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="78" eb="80">
+      <t>イコウ</t>
+    </rPh>
+    <rPh sb="86" eb="88">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージの追加</t>
+    <rPh sb="5" eb="7">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>第一ステージが完成したら次のステージを追加する</t>
+    <rPh sb="0" eb="2">
+      <t>ダイイチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カンセイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージシーン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ追加</t>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ステージ追加はアセットがあるかもしれないので、それを確認するまで作らないほうがいい</t>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bgm,SEを追加する</t>
+    <rPh sb="7" eb="9">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bgm,SEの追加</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SE</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>bgm,SEは専用のサイトがあると思うので早急に見つけること</t>
+    <rPh sb="7" eb="9">
+      <t>センヨウ</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>オモ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ソウキュウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>ミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -325,7 +647,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,6 +676,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -384,7 +714,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -394,6 +724,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -733,10 +1072,11 @@
   <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.59765625" customWidth="1"/>
+    <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="52" customWidth="1"/>
     <col min="3" max="3" width="40.19921875" customWidth="1"/>
-    <col min="6" max="6" width="69.796875" customWidth="1"/>
+    <col min="5" max="5" width="13.8984375" customWidth="1"/>
+    <col min="6" max="6" width="74.8984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -865,33 +1205,117 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>24</v>
+      </c>
       <c r="D8" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="E8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
       <c r="D9" s="2" t="b">
         <v>0</v>
       </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>40</v>
+      </c>
       <c r="D10" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="D11" s="2" t="b">
-        <v>0</v>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
       <c r="D12" s="2" t="b">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" t="s">
+        <v>54</v>
+      </c>
       <c r="D13" s="2" t="b">
         <v>0</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
